--- a/artfynd/A 34371-2019 artfynd.xlsx
+++ b/artfynd/A 34371-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 34371-2019 artfynd.xlsx
+++ b/artfynd/A 34371-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2144,6 +2144,924 @@
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>121477022</v>
+      </c>
+      <c r="B15" t="n">
+        <v>90727</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Jiltjaurberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>583601</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7272027</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2020-01-15</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2020-01-17</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Isak Sarac</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>121477021</v>
+      </c>
+      <c r="B16" t="n">
+        <v>90727</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Jiltjaurberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>584047</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7272014</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2020-01-15</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2020-01-17</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Isak Sarac</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>121477278</v>
+      </c>
+      <c r="B17" t="n">
+        <v>78604</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Jiltjaurberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>583728</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7272015</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2020-01-15</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2020-01-17</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Isak Sarac</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>121477019</v>
+      </c>
+      <c r="B18" t="n">
+        <v>90727</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Jiltjaurberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>583672</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7272007</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2020-01-15</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2020-01-17</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Isak Sarac</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>121477023</v>
+      </c>
+      <c r="B19" t="n">
+        <v>90727</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Jiltjaurberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>584012</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7272071</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2020-01-15</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2020-01-17</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Isak Sarac</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>121477020</v>
+      </c>
+      <c r="B20" t="n">
+        <v>90727</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Jiltjaurberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>583639</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7272007</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2020-01-15</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2020-01-17</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Isak Sarac</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>121476741</v>
+      </c>
+      <c r="B21" t="n">
+        <v>77945</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>498</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Liten sotlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Acolium karelicum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Jiltjaurberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>583612</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7272023</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2020-01-15</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2020-01-17</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Isak Sarac</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>121477403</v>
+      </c>
+      <c r="B22" t="n">
+        <v>88031</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>510</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Jiltjaurberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>583728</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7272015</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2020-01-15</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2020-01-17</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Isak Sarac</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>121477277</v>
+      </c>
+      <c r="B23" t="n">
+        <v>78604</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Jiltjaurberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>583755</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7272014</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2020-01-15</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2020-01-17</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Isak Sarac</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34371-2019 artfynd.xlsx
+++ b/artfynd/A 34371-2019 artfynd.xlsx
@@ -2149,7 +2149,7 @@
         <v>121477022</v>
       </c>
       <c r="B15" t="n">
-        <v>90727</v>
+        <v>90728</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2248,10 +2248,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121477021</v>
+        <v>121476741</v>
       </c>
       <c r="B16" t="n">
-        <v>90727</v>
+        <v>77945</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2260,25 +2260,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2288,10 +2288,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>584047</v>
+        <v>583612</v>
       </c>
       <c r="R16" t="n">
-        <v>7272014</v>
+        <v>7272023</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2350,10 +2350,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121477278</v>
+        <v>121477023</v>
       </c>
       <c r="B17" t="n">
-        <v>78604</v>
+        <v>90728</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2366,21 +2366,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2390,10 +2390,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>583728</v>
+        <v>584012</v>
       </c>
       <c r="R17" t="n">
-        <v>7272015</v>
+        <v>7272071</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2452,10 +2452,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121477019</v>
+        <v>121477403</v>
       </c>
       <c r="B18" t="n">
-        <v>90727</v>
+        <v>88031</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2468,21 +2468,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2492,10 +2492,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>583672</v>
+        <v>583728</v>
       </c>
       <c r="R18" t="n">
-        <v>7272007</v>
+        <v>7272015</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2554,10 +2554,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121477023</v>
+        <v>121477021</v>
       </c>
       <c r="B19" t="n">
-        <v>90727</v>
+        <v>90728</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2594,10 +2594,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>584012</v>
+        <v>584047</v>
       </c>
       <c r="R19" t="n">
-        <v>7272071</v>
+        <v>7272014</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2659,7 +2659,7 @@
         <v>121477020</v>
       </c>
       <c r="B20" t="n">
-        <v>90727</v>
+        <v>90728</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2758,10 +2758,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121476741</v>
+        <v>121477277</v>
       </c>
       <c r="B21" t="n">
-        <v>77945</v>
+        <v>78604</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2770,25 +2770,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>498</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2798,10 +2798,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>583612</v>
+        <v>583755</v>
       </c>
       <c r="R21" t="n">
-        <v>7272023</v>
+        <v>7272014</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2860,10 +2860,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121477403</v>
+        <v>121477278</v>
       </c>
       <c r="B22" t="n">
-        <v>88031</v>
+        <v>78604</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2876,21 +2876,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2962,10 +2962,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121477277</v>
+        <v>121477019</v>
       </c>
       <c r="B23" t="n">
-        <v>78604</v>
+        <v>90728</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2978,21 +2978,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3002,10 +3002,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>583755</v>
+        <v>583672</v>
       </c>
       <c r="R23" t="n">
-        <v>7272014</v>
+        <v>7272007</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 34371-2019 artfynd.xlsx
+++ b/artfynd/A 34371-2019 artfynd.xlsx
@@ -2146,10 +2146,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121477022</v>
+        <v>121477020</v>
       </c>
       <c r="B15" t="n">
-        <v>90728</v>
+        <v>90731</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2186,10 +2186,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>583601</v>
+        <v>583639</v>
       </c>
       <c r="R15" t="n">
-        <v>7272027</v>
+        <v>7272007</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2248,10 +2248,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121476741</v>
+        <v>121477403</v>
       </c>
       <c r="B16" t="n">
-        <v>77945</v>
+        <v>88034</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2260,25 +2260,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>498</v>
+        <v>510</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2288,10 +2288,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>583612</v>
+        <v>583728</v>
       </c>
       <c r="R16" t="n">
-        <v>7272023</v>
+        <v>7272015</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2350,10 +2350,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121477023</v>
+        <v>121476741</v>
       </c>
       <c r="B17" t="n">
-        <v>90728</v>
+        <v>77948</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2362,25 +2362,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2390,10 +2390,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>584012</v>
+        <v>583612</v>
       </c>
       <c r="R17" t="n">
-        <v>7272071</v>
+        <v>7272023</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2452,10 +2452,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121477403</v>
+        <v>121477019</v>
       </c>
       <c r="B18" t="n">
-        <v>88031</v>
+        <v>90731</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2468,21 +2468,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>510</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2492,10 +2492,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>583728</v>
+        <v>583672</v>
       </c>
       <c r="R18" t="n">
-        <v>7272015</v>
+        <v>7272007</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2557,7 +2557,7 @@
         <v>121477021</v>
       </c>
       <c r="B19" t="n">
-        <v>90728</v>
+        <v>90731</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2656,10 +2656,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121477020</v>
+        <v>121477022</v>
       </c>
       <c r="B20" t="n">
-        <v>90728</v>
+        <v>90731</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2696,10 +2696,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>583639</v>
+        <v>583601</v>
       </c>
       <c r="R20" t="n">
-        <v>7272007</v>
+        <v>7272027</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2758,10 +2758,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121477277</v>
+        <v>121477023</v>
       </c>
       <c r="B21" t="n">
-        <v>78604</v>
+        <v>90731</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2774,21 +2774,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2798,10 +2798,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>583755</v>
+        <v>584012</v>
       </c>
       <c r="R21" t="n">
-        <v>7272014</v>
+        <v>7272071</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2863,7 +2863,7 @@
         <v>121477278</v>
       </c>
       <c r="B22" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2962,10 +2962,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121477019</v>
+        <v>121477277</v>
       </c>
       <c r="B23" t="n">
-        <v>90728</v>
+        <v>78607</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2978,21 +2978,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3002,10 +3002,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>583672</v>
+        <v>583755</v>
       </c>
       <c r="R23" t="n">
-        <v>7272007</v>
+        <v>7272014</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 34371-2019 artfynd.xlsx
+++ b/artfynd/A 34371-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2146,7 +2146,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121477020</v>
+        <v>121477021</v>
       </c>
       <c r="B15" t="n">
         <v>90731</v>
@@ -2186,10 +2186,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>583639</v>
+        <v>584047</v>
       </c>
       <c r="R15" t="n">
-        <v>7272007</v>
+        <v>7272014</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2248,10 +2248,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121477403</v>
+        <v>121476741</v>
       </c>
       <c r="B16" t="n">
-        <v>88034</v>
+        <v>77948</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2260,25 +2260,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>510</v>
+        <v>498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2288,10 +2288,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>583728</v>
+        <v>583612</v>
       </c>
       <c r="R16" t="n">
-        <v>7272015</v>
+        <v>7272023</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2350,10 +2350,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121476741</v>
+        <v>121477403</v>
       </c>
       <c r="B17" t="n">
-        <v>77948</v>
+        <v>88034</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2362,25 +2362,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>498</v>
+        <v>510</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2390,10 +2390,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>583612</v>
+        <v>583728</v>
       </c>
       <c r="R17" t="n">
-        <v>7272023</v>
+        <v>7272015</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2452,10 +2452,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121477019</v>
+        <v>121477277</v>
       </c>
       <c r="B18" t="n">
-        <v>90731</v>
+        <v>78607</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2468,21 +2468,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2492,10 +2492,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>583672</v>
+        <v>583755</v>
       </c>
       <c r="R18" t="n">
-        <v>7272007</v>
+        <v>7272014</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2554,10 +2554,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121477021</v>
+        <v>121477278</v>
       </c>
       <c r="B19" t="n">
-        <v>90731</v>
+        <v>78607</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2570,21 +2570,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2594,10 +2594,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>584047</v>
+        <v>583728</v>
       </c>
       <c r="R19" t="n">
-        <v>7272014</v>
+        <v>7272015</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2656,7 +2656,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121477022</v>
+        <v>121477020</v>
       </c>
       <c r="B20" t="n">
         <v>90731</v>
@@ -2696,10 +2696,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>583601</v>
+        <v>583639</v>
       </c>
       <c r="R20" t="n">
-        <v>7272027</v>
+        <v>7272007</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2758,7 +2758,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121477023</v>
+        <v>121477022</v>
       </c>
       <c r="B21" t="n">
         <v>90731</v>
@@ -2798,10 +2798,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>584012</v>
+        <v>583601</v>
       </c>
       <c r="R21" t="n">
-        <v>7272071</v>
+        <v>7272027</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2860,10 +2860,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121477278</v>
+        <v>121477019</v>
       </c>
       <c r="B22" t="n">
-        <v>78607</v>
+        <v>90731</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2876,21 +2876,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2900,10 +2900,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>583728</v>
+        <v>583672</v>
       </c>
       <c r="R22" t="n">
-        <v>7272015</v>
+        <v>7272007</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2962,10 +2962,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121477277</v>
+        <v>121477023</v>
       </c>
       <c r="B23" t="n">
-        <v>78607</v>
+        <v>90731</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2978,21 +2978,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3002,10 +3002,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>583755</v>
+        <v>584012</v>
       </c>
       <c r="R23" t="n">
-        <v>7272014</v>
+        <v>7272071</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3061,6 +3061,586 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>121532809</v>
+      </c>
+      <c r="B24" t="n">
+        <v>90731</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Sorsele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>584011</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7272070</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Max Jonsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Max Jonsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>121532806</v>
+      </c>
+      <c r="B25" t="n">
+        <v>90731</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Sorsele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>583638</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7272007</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Max Jonsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Max Jonsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>121532807</v>
+      </c>
+      <c r="B26" t="n">
+        <v>90731</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Sorsele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>584046</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7272013</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Max Jonsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Max Jonsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>121532808</v>
+      </c>
+      <c r="B27" t="n">
+        <v>90731</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Sorsele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>583601</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7272026</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Max Jonsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Max Jonsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>121532188</v>
+      </c>
+      <c r="B28" t="n">
+        <v>77948</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>498</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Liten sotlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Acolium karelicum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Sorsele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>583611</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7272023</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Max Jonsson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Max Jonsson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34371-2019 artfynd.xlsx
+++ b/artfynd/A 34371-2019 artfynd.xlsx
@@ -2146,10 +2146,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121477021</v>
+        <v>121477023</v>
       </c>
       <c r="B15" t="n">
-        <v>90731</v>
+        <v>90737</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2186,10 +2186,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>584047</v>
+        <v>584012</v>
       </c>
       <c r="R15" t="n">
-        <v>7272014</v>
+        <v>7272071</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2248,10 +2248,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121476741</v>
+        <v>121477020</v>
       </c>
       <c r="B16" t="n">
-        <v>77948</v>
+        <v>90737</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2260,25 +2260,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>498</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2288,10 +2288,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>583612</v>
+        <v>583639</v>
       </c>
       <c r="R16" t="n">
-        <v>7272023</v>
+        <v>7272007</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2350,10 +2350,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121477403</v>
+        <v>121477019</v>
       </c>
       <c r="B17" t="n">
-        <v>88034</v>
+        <v>90737</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2366,21 +2366,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>510</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2390,10 +2390,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>583728</v>
+        <v>583672</v>
       </c>
       <c r="R17" t="n">
-        <v>7272015</v>
+        <v>7272007</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2452,10 +2452,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121477277</v>
+        <v>121477403</v>
       </c>
       <c r="B18" t="n">
-        <v>78607</v>
+        <v>88038</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2468,21 +2468,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2492,10 +2492,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>583755</v>
+        <v>583728</v>
       </c>
       <c r="R18" t="n">
-        <v>7272014</v>
+        <v>7272015</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2554,10 +2554,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121477278</v>
+        <v>121476741</v>
       </c>
       <c r="B19" t="n">
-        <v>78607</v>
+        <v>77949</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2566,25 +2566,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>498</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2594,10 +2594,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>583728</v>
+        <v>583612</v>
       </c>
       <c r="R19" t="n">
-        <v>7272015</v>
+        <v>7272023</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2656,10 +2656,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121477020</v>
+        <v>121477278</v>
       </c>
       <c r="B20" t="n">
-        <v>90731</v>
+        <v>78608</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2672,21 +2672,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2696,10 +2696,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>583639</v>
+        <v>583728</v>
       </c>
       <c r="R20" t="n">
-        <v>7272007</v>
+        <v>7272015</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2758,10 +2758,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121477022</v>
+        <v>121477277</v>
       </c>
       <c r="B21" t="n">
-        <v>90731</v>
+        <v>78608</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2774,21 +2774,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2798,10 +2798,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>583601</v>
+        <v>583755</v>
       </c>
       <c r="R21" t="n">
-        <v>7272027</v>
+        <v>7272014</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2860,10 +2860,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121477019</v>
+        <v>121477022</v>
       </c>
       <c r="B22" t="n">
-        <v>90731</v>
+        <v>90737</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2900,10 +2900,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>583672</v>
+        <v>583601</v>
       </c>
       <c r="R22" t="n">
-        <v>7272007</v>
+        <v>7272027</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2962,10 +2962,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121477023</v>
+        <v>121477021</v>
       </c>
       <c r="B23" t="n">
-        <v>90731</v>
+        <v>90737</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3002,10 +3002,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>584012</v>
+        <v>584047</v>
       </c>
       <c r="R23" t="n">
-        <v>7272071</v>
+        <v>7272014</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3064,10 +3064,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121532809</v>
+        <v>121532806</v>
       </c>
       <c r="B24" t="n">
-        <v>90731</v>
+        <v>90737</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3108,10 +3108,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>584011</v>
+        <v>583638</v>
       </c>
       <c r="R24" t="n">
-        <v>7272070</v>
+        <v>7272007</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3143,7 +3143,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3180,10 +3180,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121532806</v>
+        <v>121532188</v>
       </c>
       <c r="B25" t="n">
-        <v>90731</v>
+        <v>77949</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3192,25 +3192,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3224,10 +3224,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>583638</v>
+        <v>583611</v>
       </c>
       <c r="R25" t="n">
-        <v>7272007</v>
+        <v>7272023</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3269,7 +3269,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3296,10 +3296,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121532807</v>
+        <v>121532808</v>
       </c>
       <c r="B26" t="n">
-        <v>90731</v>
+        <v>90737</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3340,10 +3340,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>584046</v>
+        <v>583601</v>
       </c>
       <c r="R26" t="n">
-        <v>7272013</v>
+        <v>7272026</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3375,7 +3375,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3412,10 +3412,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121532808</v>
+        <v>121532807</v>
       </c>
       <c r="B27" t="n">
-        <v>90731</v>
+        <v>90737</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3456,10 +3456,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>583601</v>
+        <v>584046</v>
       </c>
       <c r="R27" t="n">
-        <v>7272026</v>
+        <v>7272013</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3491,7 +3491,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3501,7 +3501,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3528,10 +3528,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121532188</v>
+        <v>121532809</v>
       </c>
       <c r="B28" t="n">
-        <v>77948</v>
+        <v>90737</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3540,25 +3540,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>498</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3572,10 +3572,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>583611</v>
+        <v>584011</v>
       </c>
       <c r="R28" t="n">
-        <v>7272023</v>
+        <v>7272070</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3607,7 +3607,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3617,7 +3617,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 34371-2019 artfynd.xlsx
+++ b/artfynd/A 34371-2019 artfynd.xlsx
@@ -2146,10 +2146,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121477023</v>
+        <v>121477019</v>
       </c>
       <c r="B15" t="n">
-        <v>90737</v>
+        <v>90738</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2186,10 +2186,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>584012</v>
+        <v>583672</v>
       </c>
       <c r="R15" t="n">
-        <v>7272071</v>
+        <v>7272007</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2248,10 +2248,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121477020</v>
+        <v>121477021</v>
       </c>
       <c r="B16" t="n">
-        <v>90737</v>
+        <v>90738</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2288,10 +2288,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>583639</v>
+        <v>584047</v>
       </c>
       <c r="R16" t="n">
-        <v>7272007</v>
+        <v>7272014</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2350,10 +2350,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121477019</v>
+        <v>121477022</v>
       </c>
       <c r="B17" t="n">
-        <v>90737</v>
+        <v>90738</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2390,10 +2390,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>583672</v>
+        <v>583601</v>
       </c>
       <c r="R17" t="n">
-        <v>7272007</v>
+        <v>7272027</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2452,10 +2452,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121477403</v>
+        <v>121477278</v>
       </c>
       <c r="B18" t="n">
-        <v>88038</v>
+        <v>78609</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2468,21 +2468,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2557,7 +2557,7 @@
         <v>121476741</v>
       </c>
       <c r="B19" t="n">
-        <v>77949</v>
+        <v>77950</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2656,10 +2656,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121477278</v>
+        <v>121477023</v>
       </c>
       <c r="B20" t="n">
-        <v>78608</v>
+        <v>90738</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2672,21 +2672,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2696,10 +2696,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>583728</v>
+        <v>584012</v>
       </c>
       <c r="R20" t="n">
-        <v>7272015</v>
+        <v>7272071</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2761,7 +2761,7 @@
         <v>121477277</v>
       </c>
       <c r="B21" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2860,10 +2860,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121477022</v>
+        <v>121477020</v>
       </c>
       <c r="B22" t="n">
-        <v>90737</v>
+        <v>90738</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2900,10 +2900,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>583601</v>
+        <v>583639</v>
       </c>
       <c r="R22" t="n">
-        <v>7272027</v>
+        <v>7272007</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2962,10 +2962,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121477021</v>
+        <v>121477403</v>
       </c>
       <c r="B23" t="n">
-        <v>90737</v>
+        <v>88039</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2978,21 +2978,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3002,10 +3002,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>584047</v>
+        <v>583728</v>
       </c>
       <c r="R23" t="n">
-        <v>7272014</v>
+        <v>7272015</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3064,10 +3064,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121532806</v>
+        <v>121532807</v>
       </c>
       <c r="B24" t="n">
-        <v>90737</v>
+        <v>90738</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3108,10 +3108,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>583638</v>
+        <v>584046</v>
       </c>
       <c r="R24" t="n">
-        <v>7272007</v>
+        <v>7272013</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3143,7 +3143,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3180,10 +3180,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121532188</v>
+        <v>121532809</v>
       </c>
       <c r="B25" t="n">
-        <v>77949</v>
+        <v>90738</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3192,25 +3192,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>498</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3224,10 +3224,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>583611</v>
+        <v>584011</v>
       </c>
       <c r="R25" t="n">
-        <v>7272023</v>
+        <v>7272070</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3269,7 +3269,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3296,10 +3296,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121532808</v>
+        <v>121532188</v>
       </c>
       <c r="B26" t="n">
-        <v>90737</v>
+        <v>77950</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3308,25 +3308,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3340,10 +3340,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>583601</v>
+        <v>583611</v>
       </c>
       <c r="R26" t="n">
-        <v>7272026</v>
+        <v>7272023</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3375,7 +3375,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3412,10 +3412,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121532807</v>
+        <v>121532806</v>
       </c>
       <c r="B27" t="n">
-        <v>90737</v>
+        <v>90738</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3456,10 +3456,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>584046</v>
+        <v>583638</v>
       </c>
       <c r="R27" t="n">
-        <v>7272013</v>
+        <v>7272007</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3491,7 +3491,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3501,7 +3501,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3528,10 +3528,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121532809</v>
+        <v>121532808</v>
       </c>
       <c r="B28" t="n">
-        <v>90737</v>
+        <v>90738</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3572,10 +3572,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>584011</v>
+        <v>583601</v>
       </c>
       <c r="R28" t="n">
-        <v>7272070</v>
+        <v>7272026</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3607,7 +3607,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3617,7 +3617,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 34371-2019 artfynd.xlsx
+++ b/artfynd/A 34371-2019 artfynd.xlsx
@@ -2146,7 +2146,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121477019</v>
+        <v>121477020</v>
       </c>
       <c r="B15" t="n">
         <v>90738</v>
@@ -2186,7 +2186,7 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>583672</v>
+        <v>583639</v>
       </c>
       <c r="R15" t="n">
         <v>7272007</v>
@@ -2248,10 +2248,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121477021</v>
+        <v>121477278</v>
       </c>
       <c r="B16" t="n">
-        <v>90738</v>
+        <v>78609</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2264,21 +2264,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2288,10 +2288,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>584047</v>
+        <v>583728</v>
       </c>
       <c r="R16" t="n">
-        <v>7272014</v>
+        <v>7272015</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2350,7 +2350,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121477022</v>
+        <v>121477023</v>
       </c>
       <c r="B17" t="n">
         <v>90738</v>
@@ -2390,10 +2390,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>583601</v>
+        <v>584012</v>
       </c>
       <c r="R17" t="n">
-        <v>7272027</v>
+        <v>7272071</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2452,10 +2452,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121477278</v>
+        <v>121477403</v>
       </c>
       <c r="B18" t="n">
-        <v>78609</v>
+        <v>88039</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2468,21 +2468,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2656,7 +2656,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121477023</v>
+        <v>121477019</v>
       </c>
       <c r="B20" t="n">
         <v>90738</v>
@@ -2696,10 +2696,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>584012</v>
+        <v>583672</v>
       </c>
       <c r="R20" t="n">
-        <v>7272071</v>
+        <v>7272007</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2758,10 +2758,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121477277</v>
+        <v>121477022</v>
       </c>
       <c r="B21" t="n">
-        <v>78609</v>
+        <v>90738</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2774,21 +2774,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2798,10 +2798,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>583755</v>
+        <v>583601</v>
       </c>
       <c r="R21" t="n">
-        <v>7272014</v>
+        <v>7272027</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2860,10 +2860,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121477020</v>
+        <v>121477277</v>
       </c>
       <c r="B22" t="n">
-        <v>90738</v>
+        <v>78609</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2876,21 +2876,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2900,10 +2900,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>583639</v>
+        <v>583755</v>
       </c>
       <c r="R22" t="n">
-        <v>7272007</v>
+        <v>7272014</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2962,10 +2962,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121477403</v>
+        <v>121477021</v>
       </c>
       <c r="B23" t="n">
-        <v>88039</v>
+        <v>90738</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2978,21 +2978,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>510</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3002,10 +3002,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>583728</v>
+        <v>584047</v>
       </c>
       <c r="R23" t="n">
-        <v>7272015</v>
+        <v>7272014</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3064,7 +3064,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121532807</v>
+        <v>121532806</v>
       </c>
       <c r="B24" t="n">
         <v>90738</v>
@@ -3108,10 +3108,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>584046</v>
+        <v>583638</v>
       </c>
       <c r="R24" t="n">
-        <v>7272013</v>
+        <v>7272007</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3143,7 +3143,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3180,10 +3180,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121532809</v>
+        <v>121532188</v>
       </c>
       <c r="B25" t="n">
-        <v>90738</v>
+        <v>77950</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3192,25 +3192,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3224,10 +3224,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>584011</v>
+        <v>583611</v>
       </c>
       <c r="R25" t="n">
-        <v>7272070</v>
+        <v>7272023</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3269,7 +3269,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3296,10 +3296,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121532188</v>
+        <v>121532809</v>
       </c>
       <c r="B26" t="n">
-        <v>77950</v>
+        <v>90738</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3308,25 +3308,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>498</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3340,10 +3340,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>583611</v>
+        <v>584011</v>
       </c>
       <c r="R26" t="n">
-        <v>7272023</v>
+        <v>7272070</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3375,7 +3375,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3412,7 +3412,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121532806</v>
+        <v>121532807</v>
       </c>
       <c r="B27" t="n">
         <v>90738</v>
@@ -3456,10 +3456,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>583638</v>
+        <v>584046</v>
       </c>
       <c r="R27" t="n">
-        <v>7272007</v>
+        <v>7272013</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3491,7 +3491,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3501,7 +3501,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 34371-2019 artfynd.xlsx
+++ b/artfynd/A 34371-2019 artfynd.xlsx
@@ -2146,10 +2146,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121477020</v>
+        <v>121477277</v>
       </c>
       <c r="B15" t="n">
-        <v>90738</v>
+        <v>78609</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2162,21 +2162,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2186,10 +2186,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>583639</v>
+        <v>583755</v>
       </c>
       <c r="R15" t="n">
-        <v>7272007</v>
+        <v>7272014</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2248,10 +2248,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121477278</v>
+        <v>121477021</v>
       </c>
       <c r="B16" t="n">
-        <v>78609</v>
+        <v>90738</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2264,21 +2264,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2288,10 +2288,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>583728</v>
+        <v>584047</v>
       </c>
       <c r="R16" t="n">
-        <v>7272015</v>
+        <v>7272014</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2350,7 +2350,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121477023</v>
+        <v>121477022</v>
       </c>
       <c r="B17" t="n">
         <v>90738</v>
@@ -2390,10 +2390,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>584012</v>
+        <v>583601</v>
       </c>
       <c r="R17" t="n">
-        <v>7272071</v>
+        <v>7272027</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2452,10 +2452,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121477403</v>
+        <v>121476741</v>
       </c>
       <c r="B18" t="n">
-        <v>88039</v>
+        <v>77950</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2464,25 +2464,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>510</v>
+        <v>498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2492,10 +2492,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>583728</v>
+        <v>583612</v>
       </c>
       <c r="R18" t="n">
-        <v>7272015</v>
+        <v>7272023</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2554,10 +2554,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121476741</v>
+        <v>121477278</v>
       </c>
       <c r="B19" t="n">
-        <v>77950</v>
+        <v>78609</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2566,25 +2566,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>498</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2594,10 +2594,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>583612</v>
+        <v>583728</v>
       </c>
       <c r="R19" t="n">
-        <v>7272023</v>
+        <v>7272015</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2656,7 +2656,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121477019</v>
+        <v>121477023</v>
       </c>
       <c r="B20" t="n">
         <v>90738</v>
@@ -2696,10 +2696,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>583672</v>
+        <v>584012</v>
       </c>
       <c r="R20" t="n">
-        <v>7272007</v>
+        <v>7272071</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2758,7 +2758,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121477022</v>
+        <v>121477020</v>
       </c>
       <c r="B21" t="n">
         <v>90738</v>
@@ -2798,10 +2798,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>583601</v>
+        <v>583639</v>
       </c>
       <c r="R21" t="n">
-        <v>7272027</v>
+        <v>7272007</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2860,10 +2860,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121477277</v>
+        <v>121477403</v>
       </c>
       <c r="B22" t="n">
-        <v>78609</v>
+        <v>88039</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2876,21 +2876,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2900,10 +2900,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>583755</v>
+        <v>583728</v>
       </c>
       <c r="R22" t="n">
-        <v>7272014</v>
+        <v>7272015</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2962,7 +2962,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121477021</v>
+        <v>121477019</v>
       </c>
       <c r="B23" t="n">
         <v>90738</v>
@@ -3002,10 +3002,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>584047</v>
+        <v>583672</v>
       </c>
       <c r="R23" t="n">
-        <v>7272014</v>
+        <v>7272007</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3064,10 +3064,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121532806</v>
+        <v>121532188</v>
       </c>
       <c r="B24" t="n">
-        <v>90738</v>
+        <v>77950</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3076,25 +3076,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>498</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3108,10 +3108,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>583638</v>
+        <v>583611</v>
       </c>
       <c r="R24" t="n">
-        <v>7272007</v>
+        <v>7272023</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3143,7 +3143,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3180,10 +3180,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121532188</v>
+        <v>121532808</v>
       </c>
       <c r="B25" t="n">
-        <v>77950</v>
+        <v>90738</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3192,25 +3192,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>498</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3224,10 +3224,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>583611</v>
+        <v>583601</v>
       </c>
       <c r="R25" t="n">
-        <v>7272023</v>
+        <v>7272026</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3269,7 +3269,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3296,7 +3296,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121532809</v>
+        <v>121532806</v>
       </c>
       <c r="B26" t="n">
         <v>90738</v>
@@ -3340,10 +3340,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>584011</v>
+        <v>583638</v>
       </c>
       <c r="R26" t="n">
-        <v>7272070</v>
+        <v>7272007</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3375,7 +3375,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3528,7 +3528,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121532808</v>
+        <v>121532809</v>
       </c>
       <c r="B28" t="n">
         <v>90738</v>
@@ -3572,10 +3572,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>583601</v>
+        <v>584011</v>
       </c>
       <c r="R28" t="n">
-        <v>7272026</v>
+        <v>7272070</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3607,7 +3607,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3617,7 +3617,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 34371-2019 artfynd.xlsx
+++ b/artfynd/A 34371-2019 artfynd.xlsx
@@ -2146,10 +2146,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121477277</v>
+        <v>121477019</v>
       </c>
       <c r="B15" t="n">
-        <v>78609</v>
+        <v>90738</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2162,21 +2162,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2186,10 +2186,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>583755</v>
+        <v>583672</v>
       </c>
       <c r="R15" t="n">
-        <v>7272014</v>
+        <v>7272007</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2248,10 +2248,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121477021</v>
+        <v>121476741</v>
       </c>
       <c r="B16" t="n">
-        <v>90738</v>
+        <v>77950</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2260,25 +2260,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2288,10 +2288,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>584047</v>
+        <v>583612</v>
       </c>
       <c r="R16" t="n">
-        <v>7272014</v>
+        <v>7272023</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2350,7 +2350,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121477022</v>
+        <v>121477023</v>
       </c>
       <c r="B17" t="n">
         <v>90738</v>
@@ -2390,10 +2390,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>583601</v>
+        <v>584012</v>
       </c>
       <c r="R17" t="n">
-        <v>7272027</v>
+        <v>7272071</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2452,10 +2452,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121476741</v>
+        <v>121477020</v>
       </c>
       <c r="B18" t="n">
-        <v>77950</v>
+        <v>90738</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2464,25 +2464,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>498</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2492,10 +2492,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>583612</v>
+        <v>583639</v>
       </c>
       <c r="R18" t="n">
-        <v>7272023</v>
+        <v>7272007</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2554,10 +2554,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121477278</v>
+        <v>121477403</v>
       </c>
       <c r="B19" t="n">
-        <v>78609</v>
+        <v>88039</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2570,21 +2570,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2656,10 +2656,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121477023</v>
+        <v>121477277</v>
       </c>
       <c r="B20" t="n">
-        <v>90738</v>
+        <v>78609</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2672,21 +2672,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2696,10 +2696,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>584012</v>
+        <v>583755</v>
       </c>
       <c r="R20" t="n">
-        <v>7272071</v>
+        <v>7272014</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2758,10 +2758,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121477020</v>
+        <v>121477278</v>
       </c>
       <c r="B21" t="n">
-        <v>90738</v>
+        <v>78609</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2774,21 +2774,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2798,10 +2798,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>583639</v>
+        <v>583728</v>
       </c>
       <c r="R21" t="n">
-        <v>7272007</v>
+        <v>7272015</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2860,10 +2860,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121477403</v>
+        <v>121477022</v>
       </c>
       <c r="B22" t="n">
-        <v>88039</v>
+        <v>90738</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2876,21 +2876,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>510</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2900,10 +2900,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>583728</v>
+        <v>583601</v>
       </c>
       <c r="R22" t="n">
-        <v>7272015</v>
+        <v>7272027</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2962,7 +2962,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121477019</v>
+        <v>121477021</v>
       </c>
       <c r="B23" t="n">
         <v>90738</v>
@@ -3002,10 +3002,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>583672</v>
+        <v>584047</v>
       </c>
       <c r="R23" t="n">
-        <v>7272007</v>
+        <v>7272014</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3064,10 +3064,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121532188</v>
+        <v>121532809</v>
       </c>
       <c r="B24" t="n">
-        <v>77950</v>
+        <v>90738</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3076,25 +3076,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>498</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3108,10 +3108,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>583611</v>
+        <v>584011</v>
       </c>
       <c r="R24" t="n">
-        <v>7272023</v>
+        <v>7272070</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3143,7 +3143,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3296,7 +3296,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121532806</v>
+        <v>121532807</v>
       </c>
       <c r="B26" t="n">
         <v>90738</v>
@@ -3340,10 +3340,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>583638</v>
+        <v>584046</v>
       </c>
       <c r="R26" t="n">
-        <v>7272007</v>
+        <v>7272013</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3375,7 +3375,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3412,7 +3412,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121532807</v>
+        <v>121532806</v>
       </c>
       <c r="B27" t="n">
         <v>90738</v>
@@ -3456,10 +3456,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>584046</v>
+        <v>583638</v>
       </c>
       <c r="R27" t="n">
-        <v>7272013</v>
+        <v>7272007</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3491,7 +3491,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3501,7 +3501,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3528,10 +3528,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121532809</v>
+        <v>121532188</v>
       </c>
       <c r="B28" t="n">
-        <v>90738</v>
+        <v>77950</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3540,25 +3540,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3572,10 +3572,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>584011</v>
+        <v>583611</v>
       </c>
       <c r="R28" t="n">
-        <v>7272070</v>
+        <v>7272023</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3607,7 +3607,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3617,7 +3617,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 34371-2019 artfynd.xlsx
+++ b/artfynd/A 34371-2019 artfynd.xlsx
@@ -2149,7 +2149,7 @@
         <v>121477019</v>
       </c>
       <c r="B15" t="n">
-        <v>90738</v>
+        <v>90746</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>121476741</v>
       </c>
       <c r="B16" t="n">
-        <v>77950</v>
+        <v>77957</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2350,10 +2350,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121477023</v>
+        <v>121477278</v>
       </c>
       <c r="B17" t="n">
-        <v>90738</v>
+        <v>78616</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2366,21 +2366,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2390,10 +2390,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>584012</v>
+        <v>583728</v>
       </c>
       <c r="R17" t="n">
-        <v>7272071</v>
+        <v>7272015</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2455,7 +2455,7 @@
         <v>121477020</v>
       </c>
       <c r="B18" t="n">
-        <v>90738</v>
+        <v>90746</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2554,10 +2554,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121477403</v>
+        <v>121477023</v>
       </c>
       <c r="B19" t="n">
-        <v>88039</v>
+        <v>90746</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2570,21 +2570,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>510</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2594,10 +2594,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>583728</v>
+        <v>584012</v>
       </c>
       <c r="R19" t="n">
-        <v>7272015</v>
+        <v>7272071</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2659,7 +2659,7 @@
         <v>121477277</v>
       </c>
       <c r="B20" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2758,10 +2758,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121477278</v>
+        <v>121477022</v>
       </c>
       <c r="B21" t="n">
-        <v>78609</v>
+        <v>90746</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2774,21 +2774,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2798,10 +2798,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>583728</v>
+        <v>583601</v>
       </c>
       <c r="R21" t="n">
-        <v>7272015</v>
+        <v>7272027</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2860,10 +2860,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121477022</v>
+        <v>121477403</v>
       </c>
       <c r="B22" t="n">
-        <v>90738</v>
+        <v>88046</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2876,21 +2876,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2900,10 +2900,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>583601</v>
+        <v>583728</v>
       </c>
       <c r="R22" t="n">
-        <v>7272027</v>
+        <v>7272015</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2965,7 +2965,7 @@
         <v>121477021</v>
       </c>
       <c r="B23" t="n">
-        <v>90738</v>
+        <v>90746</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3064,10 +3064,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121532809</v>
+        <v>121532188</v>
       </c>
       <c r="B24" t="n">
-        <v>90738</v>
+        <v>77957</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3076,25 +3076,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>498</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3108,10 +3108,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>584011</v>
+        <v>583611</v>
       </c>
       <c r="R24" t="n">
-        <v>7272070</v>
+        <v>7272023</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3143,7 +3143,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3180,10 +3180,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121532808</v>
+        <v>121532806</v>
       </c>
       <c r="B25" t="n">
-        <v>90738</v>
+        <v>90746</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3224,10 +3224,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>583601</v>
+        <v>583638</v>
       </c>
       <c r="R25" t="n">
-        <v>7272026</v>
+        <v>7272007</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3269,7 +3269,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3296,10 +3296,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121532807</v>
+        <v>121532808</v>
       </c>
       <c r="B26" t="n">
-        <v>90738</v>
+        <v>90746</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3340,10 +3340,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>584046</v>
+        <v>583601</v>
       </c>
       <c r="R26" t="n">
-        <v>7272013</v>
+        <v>7272026</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3375,7 +3375,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3412,10 +3412,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121532806</v>
+        <v>121532807</v>
       </c>
       <c r="B27" t="n">
-        <v>90738</v>
+        <v>90746</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3456,10 +3456,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>583638</v>
+        <v>584046</v>
       </c>
       <c r="R27" t="n">
-        <v>7272007</v>
+        <v>7272013</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3491,7 +3491,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3501,7 +3501,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3528,10 +3528,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121532188</v>
+        <v>121532809</v>
       </c>
       <c r="B28" t="n">
-        <v>77950</v>
+        <v>90746</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3540,25 +3540,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>498</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3572,10 +3572,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>583611</v>
+        <v>584011</v>
       </c>
       <c r="R28" t="n">
-        <v>7272023</v>
+        <v>7272070</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3607,7 +3607,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3617,7 +3617,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 34371-2019 artfynd.xlsx
+++ b/artfynd/A 34371-2019 artfynd.xlsx
@@ -2146,7 +2146,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121477022</v>
+        <v>121477021</v>
       </c>
       <c r="B15" t="n">
         <v>90746</v>
@@ -2186,10 +2186,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>583601</v>
+        <v>584047</v>
       </c>
       <c r="R15" t="n">
-        <v>7272027</v>
+        <v>7272014</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2248,7 +2248,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121477278</v>
+        <v>121477277</v>
       </c>
       <c r="B16" t="n">
         <v>78616</v>
@@ -2288,10 +2288,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>583728</v>
+        <v>583755</v>
       </c>
       <c r="R16" t="n">
-        <v>7272015</v>
+        <v>7272014</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2350,7 +2350,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121477023</v>
+        <v>121477019</v>
       </c>
       <c r="B17" t="n">
         <v>90746</v>
@@ -2390,10 +2390,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>584012</v>
+        <v>583672</v>
       </c>
       <c r="R17" t="n">
-        <v>7272071</v>
+        <v>7272007</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2452,7 +2452,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121477019</v>
+        <v>121477022</v>
       </c>
       <c r="B18" t="n">
         <v>90746</v>
@@ -2492,10 +2492,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>583672</v>
+        <v>583601</v>
       </c>
       <c r="R18" t="n">
-        <v>7272007</v>
+        <v>7272027</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2554,10 +2554,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121477403</v>
+        <v>121477023</v>
       </c>
       <c r="B19" t="n">
-        <v>88046</v>
+        <v>90746</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2570,21 +2570,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>510</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2594,10 +2594,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>583728</v>
+        <v>584012</v>
       </c>
       <c r="R19" t="n">
-        <v>7272015</v>
+        <v>7272071</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2656,10 +2656,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121476741</v>
+        <v>121477403</v>
       </c>
       <c r="B20" t="n">
-        <v>77957</v>
+        <v>88046</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2668,25 +2668,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>498</v>
+        <v>510</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2696,10 +2696,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>583612</v>
+        <v>583728</v>
       </c>
       <c r="R20" t="n">
-        <v>7272023</v>
+        <v>7272015</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2758,7 +2758,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121477277</v>
+        <v>121477278</v>
       </c>
       <c r="B21" t="n">
         <v>78616</v>
@@ -2798,10 +2798,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>583755</v>
+        <v>583728</v>
       </c>
       <c r="R21" t="n">
-        <v>7272014</v>
+        <v>7272015</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2860,10 +2860,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121477021</v>
+        <v>121476741</v>
       </c>
       <c r="B22" t="n">
-        <v>90746</v>
+        <v>77957</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2872,25 +2872,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>498</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2900,10 +2900,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>584047</v>
+        <v>583612</v>
       </c>
       <c r="R22" t="n">
-        <v>7272014</v>
+        <v>7272023</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3064,7 +3064,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121532809</v>
+        <v>121532808</v>
       </c>
       <c r="B24" t="n">
         <v>90746</v>
@@ -3108,10 +3108,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>584011</v>
+        <v>583601</v>
       </c>
       <c r="R24" t="n">
-        <v>7272070</v>
+        <v>7272026</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3143,7 +3143,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3180,7 +3180,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121532806</v>
+        <v>121532809</v>
       </c>
       <c r="B25" t="n">
         <v>90746</v>
@@ -3224,10 +3224,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>583638</v>
+        <v>584011</v>
       </c>
       <c r="R25" t="n">
-        <v>7272007</v>
+        <v>7272070</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3269,7 +3269,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3296,7 +3296,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121532808</v>
+        <v>121532807</v>
       </c>
       <c r="B26" t="n">
         <v>90746</v>
@@ -3340,10 +3340,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>583601</v>
+        <v>584046</v>
       </c>
       <c r="R26" t="n">
-        <v>7272026</v>
+        <v>7272013</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3375,7 +3375,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3412,10 +3412,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121532188</v>
+        <v>121532806</v>
       </c>
       <c r="B27" t="n">
-        <v>77957</v>
+        <v>90746</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3424,25 +3424,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>498</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3456,10 +3456,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>583611</v>
+        <v>583638</v>
       </c>
       <c r="R27" t="n">
-        <v>7272023</v>
+        <v>7272007</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3491,7 +3491,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3501,7 +3501,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3528,10 +3528,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121532807</v>
+        <v>121532188</v>
       </c>
       <c r="B28" t="n">
-        <v>90746</v>
+        <v>77957</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3540,25 +3540,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3572,10 +3572,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>584046</v>
+        <v>583611</v>
       </c>
       <c r="R28" t="n">
-        <v>7272013</v>
+        <v>7272023</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3607,7 +3607,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3617,7 +3617,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 34371-2019 artfynd.xlsx
+++ b/artfynd/A 34371-2019 artfynd.xlsx
@@ -2146,7 +2146,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121477021</v>
+        <v>121477022</v>
       </c>
       <c r="B15" t="n">
         <v>90746</v>
@@ -2186,10 +2186,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>584047</v>
+        <v>583601</v>
       </c>
       <c r="R15" t="n">
-        <v>7272014</v>
+        <v>7272027</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2248,7 +2248,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121477277</v>
+        <v>121477278</v>
       </c>
       <c r="B16" t="n">
         <v>78616</v>
@@ -2288,10 +2288,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>583755</v>
+        <v>583728</v>
       </c>
       <c r="R16" t="n">
-        <v>7272014</v>
+        <v>7272015</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2350,10 +2350,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121477019</v>
+        <v>121476741</v>
       </c>
       <c r="B17" t="n">
-        <v>90746</v>
+        <v>77957</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2362,25 +2362,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2390,10 +2390,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>583672</v>
+        <v>583612</v>
       </c>
       <c r="R17" t="n">
-        <v>7272007</v>
+        <v>7272023</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2452,7 +2452,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121477022</v>
+        <v>121477019</v>
       </c>
       <c r="B18" t="n">
         <v>90746</v>
@@ -2492,10 +2492,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>583601</v>
+        <v>583672</v>
       </c>
       <c r="R18" t="n">
-        <v>7272027</v>
+        <v>7272007</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2554,10 +2554,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121477023</v>
+        <v>121477277</v>
       </c>
       <c r="B19" t="n">
-        <v>90746</v>
+        <v>78616</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2570,21 +2570,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2594,10 +2594,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>584012</v>
+        <v>583755</v>
       </c>
       <c r="R19" t="n">
-        <v>7272071</v>
+        <v>7272014</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2656,10 +2656,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121477403</v>
+        <v>121477021</v>
       </c>
       <c r="B20" t="n">
-        <v>88046</v>
+        <v>90746</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2672,21 +2672,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>510</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2696,10 +2696,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>583728</v>
+        <v>584047</v>
       </c>
       <c r="R20" t="n">
-        <v>7272015</v>
+        <v>7272014</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2758,10 +2758,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121477278</v>
+        <v>121477403</v>
       </c>
       <c r="B21" t="n">
-        <v>78616</v>
+        <v>88046</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2774,21 +2774,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2860,10 +2860,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121476741</v>
+        <v>121477020</v>
       </c>
       <c r="B22" t="n">
-        <v>77957</v>
+        <v>90746</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2872,25 +2872,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>498</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2900,10 +2900,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>583612</v>
+        <v>583639</v>
       </c>
       <c r="R22" t="n">
-        <v>7272023</v>
+        <v>7272007</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2962,7 +2962,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121477020</v>
+        <v>121477023</v>
       </c>
       <c r="B23" t="n">
         <v>90746</v>
@@ -3002,10 +3002,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>583639</v>
+        <v>584012</v>
       </c>
       <c r="R23" t="n">
-        <v>7272007</v>
+        <v>7272071</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3064,10 +3064,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121532808</v>
+        <v>121532188</v>
       </c>
       <c r="B24" t="n">
-        <v>90746</v>
+        <v>77957</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3076,25 +3076,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>498</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3108,10 +3108,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>583601</v>
+        <v>583611</v>
       </c>
       <c r="R24" t="n">
-        <v>7272026</v>
+        <v>7272023</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3143,7 +3143,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3180,7 +3180,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121532809</v>
+        <v>121532806</v>
       </c>
       <c r="B25" t="n">
         <v>90746</v>
@@ -3224,10 +3224,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>584011</v>
+        <v>583638</v>
       </c>
       <c r="R25" t="n">
-        <v>7272070</v>
+        <v>7272007</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3269,7 +3269,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3296,7 +3296,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121532807</v>
+        <v>121532809</v>
       </c>
       <c r="B26" t="n">
         <v>90746</v>
@@ -3340,10 +3340,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>584046</v>
+        <v>584011</v>
       </c>
       <c r="R26" t="n">
-        <v>7272013</v>
+        <v>7272070</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3375,7 +3375,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3412,7 +3412,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121532806</v>
+        <v>121532808</v>
       </c>
       <c r="B27" t="n">
         <v>90746</v>
@@ -3456,10 +3456,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>583638</v>
+        <v>583601</v>
       </c>
       <c r="R27" t="n">
-        <v>7272007</v>
+        <v>7272026</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3491,7 +3491,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3501,7 +3501,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3528,10 +3528,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121532188</v>
+        <v>121532807</v>
       </c>
       <c r="B28" t="n">
-        <v>77957</v>
+        <v>90746</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3540,25 +3540,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>498</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3572,10 +3572,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>583611</v>
+        <v>584046</v>
       </c>
       <c r="R28" t="n">
-        <v>7272023</v>
+        <v>7272013</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3607,7 +3607,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3617,7 +3617,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
